--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128383390</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128383368</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128383390</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128383368</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,6 +893,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128764239</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57635</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Uddö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577845</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6396176</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Seglade tillsammans över "ön"</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128383390</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128383368</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128383390</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128383368</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128383390</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128383368</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,545 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130021552</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 42900, Uddö, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577827</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6396146</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130021269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79281</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blomskägglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Usnea florida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 42000, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577903</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6396144</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130021325</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91662</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 42000, Uddö, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577919</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6396178</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130021534</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90637</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 42000, Uddö, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577868</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6396156</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130021282</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 42000, Uddö, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577859</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6396146</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Undersidan av granlåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -1211,32 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021325</v>
+        <v>130021534</v>
       </c>
       <c r="B7" t="n">
-        <v>91662</v>
+        <v>90637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577919</v>
+        <v>577868</v>
       </c>
       <c r="R7" t="n">
-        <v>6396178</v>
+        <v>6396156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1293,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,32 +1320,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021534</v>
+        <v>130021325</v>
       </c>
       <c r="B8" t="n">
-        <v>90637</v>
+        <v>91662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577868</v>
+        <v>577919</v>
       </c>
       <c r="R8" t="n">
-        <v>6396156</v>
+        <v>6396178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,7 +1113,7 @@
         <v>130021269</v>
       </c>
       <c r="B6" t="n">
-        <v>79281</v>
+        <v>79282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>130021534</v>
       </c>
       <c r="B7" t="n">
-        <v>90637</v>
+        <v>90638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>130021325</v>
       </c>
       <c r="B8" t="n">
-        <v>91662</v>
+        <v>91663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>130021282</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,6 +1545,117 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130056564</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92259</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>uddö, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577890</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6396157</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greger Ström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Greger Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>130021552</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130021269</v>
       </c>
       <c r="B6" t="n">
-        <v>79282</v>
+        <v>79283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,32 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021534</v>
+        <v>130021325</v>
       </c>
       <c r="B7" t="n">
-        <v>90638</v>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>5321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577868</v>
+        <v>577919</v>
       </c>
       <c r="R7" t="n">
-        <v>6396156</v>
+        <v>6396178</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,32 +1325,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021325</v>
+        <v>130021534</v>
       </c>
       <c r="B8" t="n">
-        <v>91663</v>
+        <v>90655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577919</v>
+        <v>577868</v>
       </c>
       <c r="R8" t="n">
-        <v>6396178</v>
+        <v>6396156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,11 +1407,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>130021282</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130056564</v>
       </c>
       <c r="B10" t="n">
-        <v>92259</v>
+        <v>92276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -1211,32 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021534</v>
+        <v>130021325</v>
       </c>
       <c r="B7" t="n">
-        <v>90671</v>
+        <v>91698</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>5321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577868</v>
+        <v>577919</v>
       </c>
       <c r="R7" t="n">
-        <v>6396156</v>
+        <v>6396178</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,32 +1325,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021325</v>
+        <v>130021534</v>
       </c>
       <c r="B8" t="n">
-        <v>91696</v>
+        <v>90673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577919</v>
+        <v>577868</v>
       </c>
       <c r="R8" t="n">
-        <v>6396178</v>
+        <v>6396156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,11 +1407,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>130021282</v>
       </c>
       <c r="B9" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130056564</v>
       </c>
       <c r="B10" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>130021552</v>
       </c>
       <c r="B5" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130021269</v>
       </c>
       <c r="B6" t="n">
-        <v>79289</v>
+        <v>79374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,32 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021325</v>
+        <v>130021534</v>
       </c>
       <c r="B7" t="n">
-        <v>91698</v>
+        <v>90760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577919</v>
+        <v>577868</v>
       </c>
       <c r="R7" t="n">
-        <v>6396178</v>
+        <v>6396156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1293,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,32 +1320,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021534</v>
+        <v>130021325</v>
       </c>
       <c r="B8" t="n">
-        <v>90673</v>
+        <v>91785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577868</v>
+        <v>577919</v>
       </c>
       <c r="R8" t="n">
-        <v>6396156</v>
+        <v>6396178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>130021282</v>
       </c>
       <c r="B9" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130056564</v>
       </c>
       <c r="B10" t="n">
-        <v>92294</v>
+        <v>92381</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42900-2025 artfynd.xlsx
+++ b/artfynd/A 42900-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128383390</v>
+        <v>130021282</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 42900, Uddö, Sm</t>
+          <t>A 42000, Uddö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577807</v>
+        <v>577859</v>
       </c>
       <c r="R2" t="n">
-        <v>6396175</v>
+        <v>6396146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kraftigt bearbetad liggande låga</t>
+          <t>Undersidan av granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,53 +789,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128383368</v>
+        <v>130021269</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 42900, Uddö, Sm</t>
+          <t>A 42000, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577802</v>
+        <v>577903</v>
       </c>
       <c r="R3" t="n">
-        <v>6396107</v>
+        <v>6396144</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,17 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat stående torrträd</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128764239</v>
+        <v>130021534</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,49 +901,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uddö-Ankarsrum, Sm</t>
+          <t>A 42000, Uddö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577845</v>
+        <v>577868</v>
       </c>
       <c r="R4" t="n">
-        <v>6396176</v>
+        <v>6396156</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,17 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Seglade tillsammans över "ön"</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,28 +980,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021552</v>
+        <v>130021325</v>
       </c>
       <c r="B5" t="n">
-        <v>58198</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,41 +1010,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 42900, Uddö, Sm</t>
+          <t>A 42000, Uddö, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577827</v>
+        <v>577919</v>
       </c>
       <c r="R5" t="n">
-        <v>6396146</v>
+        <v>6396178</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1083,18 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130021269</v>
+        <v>130056564</v>
       </c>
       <c r="B6" t="n">
-        <v>79374</v>
+        <v>92567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1639</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,17 +1147,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 42000, Sm</t>
+          <t>uddö, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577903</v>
+        <v>577890</v>
       </c>
       <c r="R6" t="n">
-        <v>6396144</v>
+        <v>6396157</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,12 +1181,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,68 +1212,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Greger Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Greger Ström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130021534</v>
+        <v>128383368</v>
       </c>
       <c r="B7" t="n">
-        <v>90760</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 42000, Uddö, Sm</t>
+          <t>A 42900, Uddö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577868</v>
+        <v>577802</v>
       </c>
       <c r="R7" t="n">
-        <v>6396156</v>
+        <v>6396107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,12 +1297,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bearbetat stående torrträd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,7 +1316,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021325</v>
+        <v>128383390</v>
       </c>
       <c r="B8" t="n">
-        <v>91785</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,45 +1345,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 42000, Uddö, Sm</t>
+          <t>A 42900, Uddö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577919</v>
+        <v>577807</v>
       </c>
       <c r="R8" t="n">
-        <v>6396178</v>
+        <v>6396175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,17 +1407,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>Kraftigt bearbetad liggande låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1426,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,59 +1444,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021282</v>
+        <v>128764239</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 42000, Uddö, Sm</t>
+          <t>Uddö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577859</v>
+        <v>577845</v>
       </c>
       <c r="R9" t="n">
-        <v>6396146</v>
+        <v>6396176</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,17 +1521,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Undersidan av granlåga</t>
+          <t>Seglade tillsammans över "ön"</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,29 +1540,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130056564</v>
+        <v>130021552</v>
       </c>
       <c r="B10" t="n">
-        <v>92381</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,40 +1569,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>uddö, Ankarsrums säteri, Sm</t>
+          <t>A 42900, Uddö, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577890</v>
+        <v>577827</v>
       </c>
       <c r="R10" t="n">
-        <v>6396157</v>
+        <v>6396146</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,22 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,19 +1641,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Greger Ström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Greger Ström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
